--- a/branches/master/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/branches/master/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T20:00:55+00:00</t>
+    <t>2023-05-08T21:08:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/branches/master/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$58</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2090" uniqueCount="422">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2125" uniqueCount="423">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T21:08:01+00:00</t>
+    <t>2023-05-11T19:02:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>Global (Whole world)</t>
+    <t>World</t>
   </si>
   <si>
     <t>Description</t>
@@ -93,7 +93,7 @@
     <t>FHIR Version</t>
   </si>
   <si>
-    <t>4.0.1</t>
+    <t>5.0.0</t>
   </si>
   <si>
     <t>Kind</t>
@@ -105,13 +105,13 @@
     <t>Type</t>
   </si>
   <si>
-    <t>Task</t>
+    <t>Transport</t>
   </si>
   <si>
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Task</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Transport</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -237,13 +237,13 @@
     <t>Mapping: Workflow Pattern</t>
   </si>
   <si>
+    <t>Mapping: FiveWs Pattern Mapping</t>
+  </si>
+  <si>
     <t>Mapping: RIM Mapping</t>
   </si>
   <si>
-    <t>Mapping: FiveWs Pattern Mapping</t>
-  </si>
-  <si>
-    <t>Mapping: HL7 v2 Mapping</t>
+    <t>Mapping: HL7 V2 Mapping</t>
   </si>
   <si>
     <t/>
@@ -259,19 +259,22 @@
 </t>
   </si>
   <si>
-    <t>A task to be performed</t>
-  </si>
-  <si>
-    <t>A task to be performed.</t>
-  </si>
-  <si>
-    <t>Request, Event</t>
-  </si>
-  <si>
-    <t>ControlAct[moodCode=INT]</t>
-  </si>
-  <si>
-    <t>Task.id</t>
+    <t>Delivery of item</t>
+  </si>
+  <si>
+    <t>Record of transport of item.</t>
+  </si>
+  <si>
+    <t>Event,Request</t>
+  </si>
+  <si>
+    <t>workflow.order</t>
+  </si>
+  <si>
+    <t>Entity, Role, or Act,Supply[moodCode=RQO]</t>
+  </si>
+  <si>
+    <t>Transport.id</t>
   </si>
   <si>
     <t>1</t>
@@ -290,13 +293,13 @@
     <t>The logical id of the resource, as used in the URL for the resource. Once assigned, this value never changes.</t>
   </si>
   <si>
-    <t>The only time that a resource does not have an id is when it is being submitted to the server using a create operation.</t>
+    <t>Within the context of the FHIR RESTful interactions, the resource has an id except for cases like the create and conditional update. Otherwise, the use of the resouce id depends on the given use case.</t>
   </si>
   <si>
     <t>Resource.id</t>
   </si>
   <si>
-    <t>Task.meta</t>
+    <t>Transport.meta</t>
   </si>
   <si>
     <t xml:space="preserve">Meta
@@ -316,7 +319,7 @@
 </t>
   </si>
   <si>
-    <t>Task.implicitRules</t>
+    <t>Transport.implicitRules</t>
   </si>
   <si>
     <t xml:space="preserve">uri
@@ -329,13 +332,13 @@
     <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
   </si>
   <si>
-    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
+    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of its narrative along with other profiles, value sets, etc.</t>
   </si>
   <si>
     <t>Resource.implicitRules</t>
   </si>
   <si>
-    <t>Task.language</t>
+    <t>Transport.language</t>
   </si>
   <si>
     <t xml:space="preserve">code
@@ -351,19 +354,19 @@
     <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
   </si>
   <si>
-    <t>preferred</t>
-  </si>
-  <si>
-    <t>A human language.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>required</t>
+  </si>
+  <si>
+    <t>IETF language tag for a human language</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/all-languages|5.0.0</t>
   </si>
   <si>
     <t>Resource.language</t>
   </si>
   <si>
-    <t>Task.text</t>
+    <t>Transport.text</t>
   </si>
   <si>
     <t>narrative
@@ -380,16 +383,20 @@
     <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
   </si>
   <si>
-    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
+    <t>Contained resources do not have a narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
   </si>
   <si>
     <t>DomainResource.text</t>
   </si>
   <si>
+    <t xml:space="preserve">dom-6
+</t>
+  </si>
+  <si>
     <t>Act.text?</t>
   </si>
   <si>
-    <t>Task.contained</t>
+    <t>Transport.contained</t>
   </si>
   <si>
     <t>inline resources
@@ -403,19 +410,23 @@
     <t>Contained, inline Resources</t>
   </si>
   <si>
-    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
-  </si>
-  <si>
-    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
+    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, nor can they have their own independent transaction scope. This is allowed to be a Parameters resource if and only if it is referenced by a resource that provides context/meaning.</t>
+  </si>
+  <si>
+    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags in their meta elements, but SHALL NOT have security labels.</t>
   </si>
   <si>
     <t>DomainResource.contained</t>
   </si>
   <si>
+    <t>dom-2
+dom-4dom-3dom-5</t>
+  </si>
+  <si>
     <t>N/A</t>
   </si>
   <si>
-    <t>Task.extension</t>
+    <t>Transport.extension</t>
   </si>
   <si>
     <t>extensions
@@ -429,7 +440,7 @@
     <t>Additional content defined by implementations</t>
   </si>
   <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and managable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
     <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
@@ -442,58 +453,58 @@
 ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
-    <t>Task.modifierExtension</t>
+    <t>Transport.modifierExtension</t>
   </si>
   <si>
     <t>Extensions that cannot be ignored</t>
   </si>
   <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and managable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R5/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
   </si>
   <si>
-    <t>Task.identifier</t>
+    <t>Transport.identifier</t>
   </si>
   <si>
     <t xml:space="preserve">Identifier
 </t>
   </si>
   <si>
-    <t>Task Instance Identifier</t>
-  </si>
-  <si>
-    <t>The business identifier for this task.</t>
-  </si>
-  <si>
-    <t>Request.identifier, Event.identifier</t>
+    <t>External identifier</t>
+  </si>
+  <si>
+    <t>Identifier for the transport event that is used to identify it across multiple disparate systems.</t>
+  </si>
+  <si>
+    <t>This identifier is typically assigned by the dispenser, and may be used to reference the delivery when exchanging information about it with other systems.</t>
+  </si>
+  <si>
+    <t>Event.identifier</t>
   </si>
   <si>
     <t>.id</t>
   </si>
   <si>
-    <t>FiveWs.identifier</t>
-  </si>
-  <si>
-    <t>Task.instantiatesCanonical</t>
+    <t>Transport.instantiatesCanonical</t>
   </si>
   <si>
     <t xml:space="preserve">canonical(ActivityDefinition)
 </t>
   </si>
   <si>
-    <t>Formal definition of task</t>
-  </si>
-  <si>
-    <t>The URL pointing to a *FHIR*-defined protocol, guideline, orderset or other definition that is adhered to in whole or in part by this Task.</t>
-  </si>
-  <si>
-    <t>Enables a formal definition of how he task is to be performed, enabling automation.</t>
+    <t>Formal definition of transport</t>
+  </si>
+  <si>
+    <t>The URL pointing to a *FHIR*-defined protocol, guideline, orderset or other definition that is adhered to in whole or in part by this Transport.</t>
+  </si>
+  <si>
+    <t>Enables a formal definition of how the transport is to be performed, enabling automation.</t>
   </si>
   <si>
     <t>Request.instantiatesCanonical, Event.instantiatesCanonical</t>
@@ -502,29 +513,29 @@
     <t>.outboundRelationship[typeCode=DEFN].target</t>
   </si>
   <si>
-    <t>Task.instantiatesUri</t>
-  </si>
-  <si>
-    <t>The URL pointing to an *externally* maintained  protocol, guideline, orderset or other definition that is adhered to in whole or in part by this Task.</t>
-  </si>
-  <si>
-    <t>Enables a formal definition of how he task is to be performed (e.g. using BPMN, BPEL, XPDL or other formal notation to be associated with a task), enabling automation.</t>
+    <t>Transport.instantiatesUri</t>
+  </si>
+  <si>
+    <t>The URL pointing to an *externally* maintained  protocol, guideline, orderset or other definition that is adhered to in whole or in part by this Transport.</t>
+  </si>
+  <si>
+    <t>Enables a formal definition of how the transport is to be performed (e.g. using BPMN, BPEL, XPDL or other formal notation to be associated with a transport), enabling automation.</t>
   </si>
   <si>
     <t>Event.instantiatesUrl</t>
   </si>
   <si>
-    <t>Task.basedOn</t>
+    <t>Transport.basedOn</t>
   </si>
   <si>
     <t xml:space="preserve">Reference(Resource)
 </t>
   </si>
   <si>
-    <t>Request fulfilled by this task</t>
-  </si>
-  <si>
-    <t>BasedOn refers to a higher-level authorization that triggered the creation of the task.  It references a "request" resource such as a ServiceRequest, MedicationRequest, ServiceRequest, CarePlan, etc. which is distinct from the "request" resource the task is seeking to fulfill.  This latter resource is referenced by FocusOn.  For example, based on a ServiceRequest (= BasedOn), a task is created to fulfill a procedureRequest ( = FocusOn ) to collect a specimen from a patient.</t>
+    <t>Request fulfilled by this transport</t>
+  </si>
+  <si>
+    <t>BasedOn refers to a higher-level authorization that triggered the creation of the transport.  It references a "request" resource such as a ServiceRequest or Transport, which is distinct from the "request" resource the Transport is seeking to fulfill.  This latter resource is referenced by FocusOn.  For example, based on a ServiceRequest (= BasedOn), a transport is created to fulfill a procedureRequest ( = FocusOn ) to transport a specimen to the lab.</t>
   </si>
   <si>
     <t>Request.basedOn, Event.basedOn</t>
@@ -533,13 +544,13 @@
     <t>.outboundRelationship[typeCode=FLFS].target[moodCode=INT]</t>
   </si>
   <si>
-    <t>Task.groupIdentifier</t>
+    <t>Transport.groupIdentifier</t>
   </si>
   <si>
     <t>Requisition or grouper id</t>
   </si>
   <si>
-    <t>An identifier that links together multiple tasks and other requests that were created in the same context.</t>
+    <t>A shared identifier common to multiple independent Request instances that were activated/authorized more or less simultaneously by a single author.  The presence of the same identifier on each request ties those requests together and may have business ramifications in terms of reporting of results, billing, etc.  E.g. a requisition number shared by a set of lab tests ordered together, or a prescription number shared by all meds ordered at one time.</t>
   </si>
   <si>
     <t>Billing and/or reporting can be linked to whether multiple requests were created as a single unit.</t>
@@ -551,59 +562,58 @@
     <t>.inboundRelationship[typeCode=COMP].source[moodCode=INT].id</t>
   </si>
   <si>
-    <t>Task.partOf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Task)
+    <t>Transport.partOf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Transport)
 </t>
   </si>
   <si>
-    <t>Composite task</t>
-  </si>
-  <si>
-    <t>Task that this particular task is part of.</t>
-  </si>
-  <si>
-    <t>This should usually be 0..1.</t>
-  </si>
-  <si>
-    <t>Allows tasks to be broken down into sub-steps (and this division can occur independent of the original task).</t>
+    <t>Part of referenced event</t>
+  </si>
+  <si>
+    <t>A larger event of which this particular event is a component or step.</t>
+  </si>
+  <si>
+    <t>Not to be used to link an event to an Encounter - use Event.context for that.++[The allowed reference resources may be adjusted as appropriate for the event resource].</t>
+  </si>
+  <si>
+    <t>E.g. Drug administration as part of a procedure, procedure as part of observation, etc.</t>
   </si>
   <si>
     <t>Event.partOf</t>
   </si>
   <si>
-    <t>.inboundRelationship[typeCode=COMP].source[moodCode=INT]</t>
-  </si>
-  <si>
-    <t>Task.status</t>
-  </si>
-  <si>
-    <t>draft | requested | received | accepted | +</t>
-  </si>
-  <si>
-    <t>The current status of the task.</t>
-  </si>
-  <si>
-    <t>These states enable coordination of task status with off-the-shelf workflow solutions that support automation of tasks.</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/task-status|4.0.1</t>
-  </si>
-  <si>
-    <t>Request.status, Event.status</t>
-  </si>
-  <si>
-    <t>.statusCode</t>
-  </si>
-  <si>
-    <t>FiveWs.status</t>
-  </si>
-  <si>
-    <t>Task.statusReason</t>
+    <t>.inboundRelationship[typeCode=COMP].source[moodCode=EVN]</t>
+  </si>
+  <si>
+    <t>Varies by domain</t>
+  </si>
+  <si>
+    <t>Transport.status</t>
+  </si>
+  <si>
+    <t>in-progress | completed | abandoned | cancelled | planned | entered-in-error</t>
+  </si>
+  <si>
+    <t>A code specifying the state of the transport event.</t>
+  </si>
+  <si>
+    <t>Status of the transport.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/transport-status|5.0.0</t>
+  </si>
+  <si>
+    <t>Event.status</t>
+  </si>
+  <si>
+    <t>.statusCode, also existence of fulfillment events</t>
+  </si>
+  <si>
+    <t>Transport.statusReason</t>
   </si>
   <si>
     <t xml:space="preserve">CodeableConcept
@@ -613,10 +623,10 @@
     <t>Reason for current status</t>
   </si>
   <si>
-    <t>An explanation as to why this task is held, failed, was refused, etc.</t>
-  </si>
-  <si>
-    <t>This applies to the current status.  Look at the history of the task to see reasons for past statuses.</t>
+    <t>An explanation as to why this transport is held, failed, was refused, etc.</t>
+  </si>
+  <si>
+    <t>This applies to the current status.  Look at the history of the transport to see reasons for past statuses.</t>
   </si>
   <si>
     <t>example</t>
@@ -625,120 +635,105 @@
     <t>Codes to identify the reason for current status.  These will typically be specific to a particular workflow.</t>
   </si>
   <si>
+    <t>http://hl7.org/fhir/ValueSet/transport-status-reason</t>
+  </si>
+  <si>
     <t>.inboundRelationship[typeCode=SUBJ].source[classCode=CACT, moodCode=EVN, code="status change"].reasonCode</t>
   </si>
   <si>
-    <t>Task.businessStatus</t>
-  </si>
-  <si>
-    <t>E.g. "Specimen collected", "IV prepped"</t>
-  </si>
-  <si>
-    <t>Contains business-specific nuances of the business state.</t>
-  </si>
-  <si>
-    <t>There's often a need to track substates of a task - this is often variable by specific workflow implementation.</t>
-  </si>
-  <si>
-    <t>The domain-specific business-contextual sub-state of the task.  For example: "Blood drawn", "IV inserted", "Awaiting physician signature", etc.</t>
-  </si>
-  <si>
-    <t>.inboundRelationship[typeCode=SUBJ].source[classCode=OBS, moodCode=EVN, code="business status"]</t>
-  </si>
-  <si>
-    <t>Task.intent</t>
+    <t>Transport.intent</t>
   </si>
   <si>
     <t>unknown | proposal | plan | order | original-order | reflex-order | filler-order | instance-order | option</t>
   </si>
   <si>
-    <t>Indicates the "level" of actionability associated with the Task, i.e. i+R[9]Cs this a proposed task, a planned task, an actionable task, etc.</t>
-  </si>
-  <si>
-    <t>This element is immutable.  Proposed tasks, planned tasks, etc. must be distinct instances.
-In most cases, Tasks will have an intent of "order".</t>
-  </si>
-  <si>
-    <t>Distinguishes whether the task is a proposal, plan or full order.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/task-intent|4.0.1</t>
+    <t>Indicates the "level" of actionability associated with the Transport, i.e. i+R[9]Cs this a proposed transport, a planned transport, an actionable transport, etc.</t>
+  </si>
+  <si>
+    <t>This element is immutable.  Proposed transports, planned transports, etc. must be distinct instances.
+In most cases, Transports will have an intent of "order".</t>
+  </si>
+  <si>
+    <t>Distinguishes whether the transport is a proposal, plan or full order.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/transport-intent|5.0.0</t>
   </si>
   <si>
     <t>Request.intent</t>
   </si>
   <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
     <t>.moodCode</t>
   </si>
   <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>Task.priority</t>
+    <t>Transport.priority</t>
   </si>
   <si>
     <t>routine | urgent | asap | stat</t>
   </si>
   <si>
-    <t>Indicates how quickly the Task should be addressed with respect to other requests.</t>
-  </si>
-  <si>
-    <t>Used to identify the service level expected while performing a task.</t>
-  </si>
-  <si>
-    <t>If missing, this task should be performed with normal priority</t>
-  </si>
-  <si>
-    <t>The task's priority.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/request-priority|4.0.1</t>
+    <t>Indicates how quickly the Transport should be addressed with respect to other requests.</t>
+  </si>
+  <si>
+    <t>Used to identify the service level expected while performing a transport.</t>
+  </si>
+  <si>
+    <t>If missing, this transport should be performed with normal priority</t>
+  </si>
+  <si>
+    <t>The priority of a transport (may affect service level applied to the transport).</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/request-priority|5.0.0</t>
   </si>
   <si>
     <t>Request.priority</t>
   </si>
   <si>
+    <t>FiveWs.grade</t>
+  </si>
+  <si>
     <t>.priorityCode</t>
   </si>
   <si>
-    <t>FiveWs.grade</t>
-  </si>
-  <si>
-    <t>Task.code</t>
-  </si>
-  <si>
-    <t>Task Type</t>
-  </si>
-  <si>
-    <t>A name or code (or both) briefly describing what the task involves.</t>
-  </si>
-  <si>
-    <t>The title (eg "My Tasks", "Outstanding Tasks for Patient X") should go into the code.</t>
-  </si>
-  <si>
-    <t>Codes to identify what the task involves.  These will typically be specific to a particular workflow.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/task-code</t>
+    <t>Transport.code</t>
+  </si>
+  <si>
+    <t>Transport Type</t>
+  </si>
+  <si>
+    <t>A name or code (or both) briefly describing what the transport involves.</t>
+  </si>
+  <si>
+    <t>The title (eg "My Transports", "Outstanding Transports for Patient X") should go into the code.</t>
+  </si>
+  <si>
+    <t>Codes to identify what the transport involves.  These will typically be specific to a particular workflow.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/transport-code</t>
   </si>
   <si>
     <t>Request.code, Event.code</t>
   </si>
   <si>
+    <t>FiveWs.what[x]</t>
+  </si>
+  <si>
     <t>.code</t>
   </si>
   <si>
-    <t>FiveWs.what[x]</t>
-  </si>
-  <si>
-    <t>Task.description</t>
+    <t>Transport.description</t>
   </si>
   <si>
     <t xml:space="preserve">string
 </t>
   </si>
   <si>
-    <t>Human-readable explanation of task</t>
+    <t>Human-readable explanation of transport</t>
   </si>
   <si>
     <t>A free-text description of what is to be performed.</t>
@@ -747,16 +742,16 @@
     <t>.text</t>
   </si>
   <si>
-    <t>Task.focus</t>
-  </si>
-  <si>
-    <t>What task is acting on</t>
-  </si>
-  <si>
-    <t>The request being actioned or the resource being manipulated by this task.</t>
-  </si>
-  <si>
-    <t>If multiple resources need to be manipulated, use sub-tasks.  (This ensures that status can be tracked independently for each referenced resource.).</t>
+    <t>Transport.focus</t>
+  </si>
+  <si>
+    <t>What transport is acting on</t>
+  </si>
+  <si>
+    <t>The request being actioned or the resource being manipulated by this transport.</t>
+  </si>
+  <si>
+    <t>If multiple resources need to be manipulated, use sub-transports.  (This ensures that status can be tracked independently for each referenced resource.).</t>
   </si>
   <si>
     <t>Used to identify the thing to be done.</t>
@@ -765,434 +760,392 @@
     <t>.outboundRelationship[typeCode=SUBJ].target</t>
   </si>
   <si>
-    <t>Task.for</t>
+    <t>Transport.for</t>
   </si>
   <si>
     <t xml:space="preserve">Patient
 </t>
   </si>
   <si>
-    <t>Beneficiary of the Task</t>
-  </si>
-  <si>
-    <t>The entity who benefits from the performance of the service specified in the task (e.g., the patient).</t>
-  </si>
-  <si>
-    <t>Used to track tasks outstanding for a beneficiary.  Do not use to track the task owner or creator (see owner and creator respectively).  This can also affect access control.</t>
+    <t>Beneficiary of the Transport</t>
+  </si>
+  <si>
+    <t>The entity who benefits from the performance of the service specified in the transport (e.g., the patient).</t>
+  </si>
+  <si>
+    <t>Used to track transports outstanding for a beneficiary.  Do not use to track the transport owner or creator (see owner and creator respectively).  This can also affect access control.</t>
   </si>
   <si>
     <t>Request.subject, Event.subject</t>
   </si>
   <si>
+    <t>FiveWs.subject[x]</t>
+  </si>
+  <si>
     <t>.participation[typeCode=RCT].role</t>
   </si>
   <si>
-    <t>FiveWs.subject</t>
-  </si>
-  <si>
-    <t>Task.encounter</t>
+    <t>Transport.encounter</t>
   </si>
   <si>
     <t xml:space="preserve">Reference(Encounter)
 </t>
   </si>
   <si>
-    <t>Healthcare event during which this task originated</t>
-  </si>
-  <si>
-    <t>The healthcare event  (e.g. a patient and healthcare provider interaction) during which this task was created.</t>
-  </si>
-  <si>
-    <t>For some tasks it may be important to know the link between the encounter the task originated within.</t>
-  </si>
-  <si>
-    <t>Request.context, Event.context</t>
+    <t>Healthcare event during which this transport originated</t>
+  </si>
+  <si>
+    <t>The healthcare event  (e.g. a patient and healthcare provider interaction) during which this transport was created.</t>
+  </si>
+  <si>
+    <t>For some transports it may be important to know the link between the encounter the transport originated within.</t>
+  </si>
+  <si>
+    <t>Request.encounter, Event.encounter</t>
+  </si>
+  <si>
+    <t>FiveWs.context</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=COMP].source[classCode=PCPR, moodCode=EVN]</t>
   </si>
   <si>
-    <t>FiveWs.context</t>
-  </si>
-  <si>
-    <t>Task.executionPeriod</t>
+    <t>Transport.completionTime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dateTime
+</t>
+  </si>
+  <si>
+    <t>Completion time of the event (the occurrence)</t>
+  </si>
+  <si>
+    <t>Identifies the completion time of the event (the occurrence).</t>
+  </si>
+  <si>
+    <t>Event.occurrence[x]</t>
+  </si>
+  <si>
+    <t>FiveWs.done[x]</t>
+  </si>
+  <si>
+    <t>.effectiveTime</t>
+  </si>
+  <si>
+    <t>Transport.authoredOn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Created Date
+</t>
+  </si>
+  <si>
+    <t>Transport Creation Date</t>
+  </si>
+  <si>
+    <t>The date and time this transport was created.</t>
+  </si>
+  <si>
+    <t>Most often used along with lastUpdated to track duration of the transport to supporting monitoring and management.</t>
+  </si>
+  <si>
+    <t>Request.authoredOn</t>
+  </si>
+  <si>
+    <t>FiveWs.recorded</t>
+  </si>
+  <si>
+    <t>.participation[typeCode=AUT].time</t>
+  </si>
+  <si>
+    <t>Transport.lastModified</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Update Date
+</t>
+  </si>
+  <si>
+    <t>Transport Last Modified Date</t>
+  </si>
+  <si>
+    <t>The date and time of last modification to this transport.</t>
+  </si>
+  <si>
+    <t>Used along with history to track transport activity and time in a particular transport state.  This enables monitoring and management.</t>
+  </si>
+  <si>
+    <t>.inboundRelationship[typeCode=SUBJ, ].source[classCode=CACT, moodCode=EVN].effectiveTime</t>
+  </si>
+  <si>
+    <t>Transport.requester</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Device|Organization|Patient|Practitioner|PractitionerRole|RelatedPerson)
+</t>
+  </si>
+  <si>
+    <t>Who is asking for transport to be done</t>
+  </si>
+  <si>
+    <t>The creator of the transport.</t>
+  </si>
+  <si>
+    <t>Identifies who created this transport.  May be used by access control mechanisms (e.g., to ensure that only the creator can cancel a transport).</t>
+  </si>
+  <si>
+    <t>Request.requester</t>
+  </si>
+  <si>
+    <t>FiveWs.author</t>
+  </si>
+  <si>
+    <t>.participation[typeCode=AUT].role</t>
+  </si>
+  <si>
+    <t>Transport.performerType</t>
+  </si>
+  <si>
+    <t>Requested performer</t>
+  </si>
+  <si>
+    <t>The kind of participant that should perform the transport.</t>
+  </si>
+  <si>
+    <t>Use to distinguish transports on different activity queues.</t>
+  </si>
+  <si>
+    <t>preferred</t>
+  </si>
+  <si>
+    <t>The type(s) of transport performers allowed.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/performer-role</t>
+  </si>
+  <si>
+    <t>Event.performer.function, Request.performerType</t>
+  </si>
+  <si>
+    <t>FiveWs.actor</t>
+  </si>
+  <si>
+    <t>.participation[typeCode=PRF].role.code</t>
+  </si>
+  <si>
+    <t>Transport.owner</t>
+  </si>
+  <si>
+    <t>Performer
+Executer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|CareTeam|HealthcareService|Patient|Device|RelatedPerson)
+</t>
+  </si>
+  <si>
+    <t>Responsible individual</t>
+  </si>
+  <si>
+    <t>Individual organization or Device currently responsible for transport execution.</t>
+  </si>
+  <si>
+    <t>Transports may be created with an owner not yet identified.</t>
+  </si>
+  <si>
+    <t>Identifies who is expected to perform this transport.</t>
+  </si>
+  <si>
+    <t>Event.performer.actor, Request.performer</t>
+  </si>
+  <si>
+    <t>.participation[typeCode=PRF].role</t>
+  </si>
+  <si>
+    <t>Transport.location</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Location)
+</t>
+  </si>
+  <si>
+    <t>Where transport occurs</t>
+  </si>
+  <si>
+    <t>Principal physical location where this transport is performed.</t>
+  </si>
+  <si>
+    <t>Ties the event to where the records are likely kept and provides context around the event occurrence (e.g. if it occurred inside or outside a dedicated healthcare setting).</t>
+  </si>
+  <si>
+    <t>FiveWs.where[x]</t>
+  </si>
+  <si>
+    <t>.participation[typeCode=LOC].role</t>
+  </si>
+  <si>
+    <t>Transport.insurance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Coverage|ClaimResponse)
+</t>
+  </si>
+  <si>
+    <t>Associated insurance coverage</t>
+  </si>
+  <si>
+    <t>Insurance plans, coverage extensions, pre-authorizations and/or pre-determinations that may be relevant to the Transport.</t>
+  </si>
+  <si>
+    <t>Request.insurance</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode=COVBY].target</t>
+  </si>
+  <si>
+    <t>IN1/IN2</t>
+  </si>
+  <si>
+    <t>Transport.note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Annotation
+</t>
+  </si>
+  <si>
+    <t>Comments made about the transport</t>
+  </si>
+  <si>
+    <t>Free-text information captured about the transport as it progresses.</t>
+  </si>
+  <si>
+    <t>Request.note, Event.note</t>
+  </si>
+  <si>
+    <t>.inboundRelationship[typeCode=SUBJ, ].source[classCode=OBS, moodCode=EVN, code="annotation"].value(string)</t>
+  </si>
+  <si>
+    <t>Transport.relevantHistory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Status History
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Provenance)
+</t>
+  </si>
+  <si>
+    <t>Key events in history of the Transport</t>
+  </si>
+  <si>
+    <t>Links to Provenance records for past versions of this Transport that identify key state transitions or updates that are likely to be relevant to a user looking at the current version of the transport.</t>
+  </si>
+  <si>
+    <t>This element does not point to the Provenance associated with the *current* version of the resource - as it would be created after this version existed.  The Provenance for the current version can be retrieved with a _revinclude.</t>
+  </si>
+  <si>
+    <t>Request.relevantHistory</t>
+  </si>
+  <si>
+    <t>.inboundRelationship(typeCode=SUBJ].source[classCode=CACT, moodCode=EVN]</t>
+  </si>
+  <si>
+    <t>Transport.restriction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BackboneElement
+</t>
+  </si>
+  <si>
+    <t>Constraints on fulfillment transports</t>
+  </si>
+  <si>
+    <t>If the Transport.focus is a request resource and the transport is seeking fulfillment (i.e. is asking for the request to be actioned), this element identifies any limitations on what parts of the referenced request should be actioned.</t>
+  </si>
+  <si>
+    <t>Sometimes when fulfillment is sought, you don't want full fulfillment.</t>
+  </si>
+  <si>
+    <t>Instead of pointing to request, would point to component of request, having these characteristics</t>
+  </si>
+  <si>
+    <t>Transport.restriction.id</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Transport.restriction.extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and managable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Transport.restriction.modifierExtension</t>
+  </si>
+  <si>
+    <t>extensions
+user contentmodifiers</t>
+  </si>
+  <si>
+    <t>Extensions that cannot be ignored even if unrecognized</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and managable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
+  </si>
+  <si>
+    <t>BackboneElement.modifierExtension</t>
+  </si>
+  <si>
+    <t>Transport.restriction.repetitions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">positiveInt
+</t>
+  </si>
+  <si>
+    <t>How many times to repeat</t>
+  </si>
+  <si>
+    <t>Indicates the number of times the requested action should occur.</t>
+  </si>
+  <si>
+    <t>E.g. order that requests monthly lab tests, fulfillment is sought for 1.</t>
+  </si>
+  <si>
+    <t>.repeatNumber</t>
+  </si>
+  <si>
+    <t>Transport.restriction.period</t>
   </si>
   <si>
     <t xml:space="preserve">Period
 </t>
   </si>
   <si>
-    <t>Start and end time of execution</t>
-  </si>
-  <si>
-    <t>Identifies the time action was first taken against the task (start) and/or the time final action was taken against the task prior to marking it as completed (end).</t>
-  </si>
-  <si>
-    <t>Event.occurrence[x]</t>
-  </si>
-  <si>
-    <t>.effectiveTime</t>
-  </si>
-  <si>
-    <t>FiveWs.done[x]</t>
-  </si>
-  <si>
-    <t>Task.authoredOn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Created Date
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dateTime
-</t>
-  </si>
-  <si>
-    <t>Task Creation Date</t>
-  </si>
-  <si>
-    <t>The date and time this task was created.</t>
-  </si>
-  <si>
-    <t>Most often used along with lastUpdated to track duration of task to supporting monitoring and management.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">inv-1
-</t>
-  </si>
-  <si>
-    <t>Request.authoredOn</t>
-  </si>
-  <si>
-    <t>.participation[typeCode=AUT].time</t>
-  </si>
-  <si>
-    <t>FiveWs.recorded</t>
-  </si>
-  <si>
-    <t>Task.lastModified</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Update Date
-</t>
-  </si>
-  <si>
-    <t>Task Last Modified Date</t>
-  </si>
-  <si>
-    <t>The date and time of last modification to this task.</t>
-  </si>
-  <si>
-    <t>Used along with history to track task activity and time in a particular task state.  This enables monitoring and management.</t>
-  </si>
-  <si>
-    <t>.inboundRelationship[typeCode=SUBJ, ].source[classCode=CACT, moodCode=EVN].effectiveTime</t>
-  </si>
-  <si>
-    <t>Task.requester</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Device|Organization|Patient|Practitioner|PractitionerRole|RelatedPerson)
-</t>
-  </si>
-  <si>
-    <t>Who is asking for task to be done</t>
-  </si>
-  <si>
-    <t>The creator of the task.</t>
-  </si>
-  <si>
-    <t>Identifies who created this task.  May be used by access control mechanisms (e.g., to ensure that only the creator can cancel a task).</t>
-  </si>
-  <si>
-    <t>Request.requester</t>
-  </si>
-  <si>
-    <t>.participation[typeCode=AUT].role</t>
-  </si>
-  <si>
-    <t>FiveWs.author</t>
-  </si>
-  <si>
-    <t>Task.performerType</t>
-  </si>
-  <si>
-    <t>Requested performer</t>
-  </si>
-  <si>
-    <t>The kind of participant that should perform the task.</t>
-  </si>
-  <si>
-    <t>Use to distinguish tasks on different activity queues.</t>
-  </si>
-  <si>
-    <t>The type(s) of task performers allowed.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/performer-role</t>
-  </si>
-  <si>
-    <t>Event.performer.role, Request.performerType</t>
-  </si>
-  <si>
-    <t>.participation[typeCode=PRF].role.code</t>
-  </si>
-  <si>
-    <t>FiveWs.actor</t>
-  </si>
-  <si>
-    <t>Task.owner</t>
-  </si>
-  <si>
-    <t>Performer
-Executer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|CareTeam|HealthcareService|Patient|Device|RelatedPerson)
-</t>
-  </si>
-  <si>
-    <t>Responsible individual</t>
-  </si>
-  <si>
-    <t>Individual organization or Device currently responsible for task execution.</t>
-  </si>
-  <si>
-    <t>Tasks may be created with an owner not yet identified.</t>
-  </si>
-  <si>
-    <t>Identifies who is expected to perform this task.</t>
-  </si>
-  <si>
-    <t>Event.performer.actor, Request.performer</t>
-  </si>
-  <si>
-    <t>.participation[typeCode=PRF].role</t>
-  </si>
-  <si>
-    <t>Task.location</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Location)
-</t>
-  </si>
-  <si>
-    <t>Where task occurs</t>
-  </si>
-  <si>
-    <t>Principal physical location where the this task is performed.</t>
-  </si>
-  <si>
-    <t>Ties the event to where the records are likely kept and provides context around the event occurrence (e.g. if it occurred inside or outside a dedicated healthcare setting).</t>
-  </si>
-  <si>
-    <t>Request.reasonCode, Event.reasonCode</t>
-  </si>
-  <si>
-    <t>.participation[typeCode=LOC].role</t>
-  </si>
-  <si>
-    <t>FiveWs.where[x]</t>
-  </si>
-  <si>
-    <t>Task.reasonCode</t>
-  </si>
-  <si>
-    <t>Why task is needed</t>
-  </si>
-  <si>
-    <t>A description or code indicating why this task needs to be performed.</t>
-  </si>
-  <si>
-    <t>This should only be included if there is no focus or if it differs from the reason indicated on the focus.</t>
-  </si>
-  <si>
-    <t>Indicates why the task is needed.  E.g. Suspended because patient admitted to hospital.</t>
-  </si>
-  <si>
-    <t>Event.location</t>
-  </si>
-  <si>
-    <t>.reasonCode</t>
-  </si>
-  <si>
-    <t>FiveWs.why[x]</t>
-  </si>
-  <si>
-    <t>EVN.7</t>
-  </si>
-  <si>
-    <t>Task.reasonReference</t>
-  </si>
-  <si>
-    <t>A resource reference indicating why this task needs to be performed.</t>
-  </si>
-  <si>
-    <t>Tasks might be justified based on an Observation, a Condition, a past or planned procedure, etc.   This should only be included if there is no focus or if it differs from the reason indicated on the focus.    Use the CodeableConcept text element in `Task.reasonCode` if the data is free (uncoded) text.</t>
-  </si>
-  <si>
-    <t>Request.reasonReference, Event.reasonReference</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode=RSON].target</t>
-  </si>
-  <si>
-    <t>Task.insurance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Coverage|ClaimResponse)
-</t>
-  </si>
-  <si>
-    <t>Associated insurance coverage</t>
-  </si>
-  <si>
-    <t>Insurance plans, coverage extensions, pre-authorizations and/or pre-determinations that may be relevant to the Task.</t>
-  </si>
-  <si>
-    <t>Request.insurance</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode=COVBY].target</t>
-  </si>
-  <si>
-    <t>IN1/IN2</t>
-  </si>
-  <si>
-    <t>Task.note</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Annotation
-</t>
-  </si>
-  <si>
-    <t>Comments made about the task</t>
-  </si>
-  <si>
-    <t>Free-text information captured about the task as it progresses.</t>
-  </si>
-  <si>
-    <t>Request.note, Event.note</t>
-  </si>
-  <si>
-    <t>.inboundRelationship[typeCode=SUBJ, ].source[classCode=OBS, moodCode=EVN, code="annotation"].value(string)</t>
-  </si>
-  <si>
-    <t>Task.relevantHistory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Status History
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Provenance)
-</t>
-  </si>
-  <si>
-    <t>Key events in history of the Task</t>
-  </si>
-  <si>
-    <t>Links to Provenance records for past versions of this Task that identify key state transitions or updates that are likely to be relevant to a user looking at the current version of the task.</t>
-  </si>
-  <si>
-    <t>This element does not point to the Provenance associated with the *current* version of the resource - as it would be created after this version existed.  The Provenance for the current version can be retrieved with a _revinclude.</t>
-  </si>
-  <si>
-    <t>Request.relevantHistory</t>
-  </si>
-  <si>
-    <t>.inboundRelationship(typeCode=SUBJ].source[classCode=CACT, moodCode=EVN]</t>
-  </si>
-  <si>
-    <t>Task.restriction</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BackboneElement
-</t>
-  </si>
-  <si>
-    <t>Constraints on fulfillment tasks</t>
-  </si>
-  <si>
-    <t>If the Task.focus is a request resource and the task is seeking fulfillment (i.e. is asking for the request to be actioned), this element identifies any limitations on what parts of the referenced request should be actioned.</t>
-  </si>
-  <si>
-    <t>Sometimes when fulfillment is sought, you don't want full fulfillment.</t>
-  </si>
-  <si>
-    <t>Instead of pointing to request, would point to component of request, having these characteristics</t>
-  </si>
-  <si>
-    <t>Task.restriction.id</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>Task.restriction.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>Task.restriction.modifierExtension</t>
-  </si>
-  <si>
-    <t>extensions
-user contentmodifiers</t>
-  </si>
-  <si>
-    <t>Extensions that cannot be ignored even if unrecognized</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
-Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
-  </si>
-  <si>
-    <t>BackboneElement.modifierExtension</t>
-  </si>
-  <si>
-    <t>Task.restriction.repetitions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">positiveInt
-</t>
-  </si>
-  <si>
-    <t>How many times to repeat</t>
-  </si>
-  <si>
-    <t>Indicates the number of times the requested action should occur.</t>
-  </si>
-  <si>
-    <t>E.g. order that requests monthly lab tests, fulfillment is sought for 1.</t>
-  </si>
-  <si>
-    <t>.repeatNumber</t>
-  </si>
-  <si>
-    <t>Task.restriction.period</t>
-  </si>
-  <si>
     <t>When fulfillment sought</t>
   </si>
   <si>
     <t>Over what time-period is fulfillment sought.</t>
   </si>
   <si>
-    <t>Note that period.high is the due date representing the time by which the task should be completed.</t>
+    <t>Note that period.high is the due date representing the time by which the transport should be completed.</t>
   </si>
   <si>
     <t>E.g. order that authorizes 1 year's services.  Fulfillment is sought for next 3 months.</t>
@@ -1201,7 +1154,7 @@
     <t>.effectiveTime(IVL&lt;TS&gt;)</t>
   </si>
   <si>
-    <t>Task.restriction.recipient</t>
+    <t>Transport.restriction.recipient</t>
   </si>
   <si>
     <t xml:space="preserve">Reference(Patient|Practitioner|PractitionerRole|RelatedPerson|Group|Organization)
@@ -1211,41 +1164,41 @@
     <t>For whom is fulfillment sought?</t>
   </si>
   <si>
-    <t>For requests that are targeted to more than on potential recipient/target, for whom is fulfillment sought?</t>
+    <t>For requests that are targeted to more than one potential recipient/target, to identify who is fulfillment is sought for.</t>
   </si>
   <si>
     <t>.participation[typeCode=SBJ].role</t>
   </si>
   <si>
-    <t>Task.input</t>
+    <t>Transport.input</t>
   </si>
   <si>
     <t xml:space="preserve">Supporting Information
 </t>
   </si>
   <si>
-    <t>Information used to perform task</t>
-  </si>
-  <si>
-    <t>Additional information that may be needed in the execution of the task.</t>
-  </si>
-  <si>
-    <t>Resources and data used to perform the task.  This data is used in the business logic of task execution, and is stored separately because it varies between workflows.</t>
+    <t>Information used to perform transport</t>
+  </si>
+  <si>
+    <t>Additional information that may be needed in the execution of the transport.</t>
+  </si>
+  <si>
+    <t>Resources and data used to perform the transport.  This data is used in the business logic of transport execution, and is stored separately because it varies between workflows.</t>
   </si>
   <si>
     <t>???</t>
   </si>
   <si>
-    <t>Task.input.id</t>
-  </si>
-  <si>
-    <t>Task.input.extension</t>
-  </si>
-  <si>
-    <t>Task.input.modifierExtension</t>
-  </si>
-  <si>
-    <t>Task.input.type</t>
+    <t>Transport.input.id</t>
+  </si>
+  <si>
+    <t>Transport.input.extension</t>
+  </si>
+  <si>
+    <t>Transport.input.modifierExtension</t>
+  </si>
+  <si>
+    <t>Transport.input.type</t>
   </si>
   <si>
     <t xml:space="preserve">Name
@@ -1255,53 +1208,53 @@
     <t>Label for the input</t>
   </si>
   <si>
-    <t>A code or description indicating how the input is intended to be used as part of the task execution.</t>
+    <t>A code or description indicating how the input is intended to be used as part of the transport execution.</t>
   </si>
   <si>
     <t>If referencing a BPMN workflow or Protocol, the "system" is the URL for the workflow definition and the code is the "name" of the required input.</t>
   </si>
   <si>
-    <t>Inputs are named to enable task automation to bind data and pass it from one task to the next.</t>
+    <t>Inputs are named to enable transport automation to bind data and pass it from one transport to the next.</t>
   </si>
   <si>
     <t>Codes to identify types of input parameters.  These will typically be specific to a particular workflow.  E.g. "Comparison source", "Applicable consent", "Concomitent Medications", etc.</t>
   </si>
   <si>
-    <t>Task.input.value[x]</t>
+    <t>Transport.input.value[x]</t>
   </si>
   <si>
     <t>base64Binary
-booleancanonicalcodedatedateTimedecimalidinstantintegermarkdownoidpositiveIntstringtimeunsignedInturiurluuidAddressAgeAnnotationAttachmentCodeableConceptCodingContactPointCountDistanceDurationHumanNameIdentifierMoneyPeriodQuantityRangeRatioReferenceSampledDataSignatureTimingContactDetailContributorDataRequirementExpressionParameterDefinitionRelatedArtifactTriggerDefinitionUsageContextDosageMeta</t>
-  </si>
-  <si>
-    <t>Content to use in performing the task</t>
+booleancanonicalcodedatedateTimedecimalidinstantintegerinteger64markdownoidpositiveIntstringtimeunsignedInturiurluuidAddressAgeAnnotationAttachmentCodeableConceptCodeableReferenceCodingContactPointCountDistanceDurationHumanNameIdentifierMoneyPeriodQuantityRangeRatioRatioRangeReferenceSampledDataSignatureTimingContactDetailDataRequirementExpressionParameterDefinitionRelatedArtifactTriggerDefinitionUsageContextAvailabilityExtendedContactDetailDosageMeta</t>
+  </si>
+  <si>
+    <t>Content to use in performing the transport</t>
   </si>
   <si>
     <t>The value of the input parameter as a basic type.</t>
   </si>
   <si>
-    <t>Task.output</t>
-  </si>
-  <si>
-    <t>Information produced as part of task</t>
-  </si>
-  <si>
-    <t>Outputs produced by the Task.</t>
-  </si>
-  <si>
-    <t>Resources and data produced during the execution the task.  This data is generated by the business logic of task execution, and is stored separately because it varies between workflows.</t>
-  </si>
-  <si>
-    <t>Task.output.id</t>
-  </si>
-  <si>
-    <t>Task.output.extension</t>
-  </si>
-  <si>
-    <t>Task.output.modifierExtension</t>
-  </si>
-  <si>
-    <t>Task.output.type</t>
+    <t>Transport.output</t>
+  </si>
+  <si>
+    <t>Information produced as part of transport</t>
+  </si>
+  <si>
+    <t>Outputs produced by the Transport.</t>
+  </si>
+  <si>
+    <t>Resources and data produced during the execution the transport.  This data is generated by the business logic of transport execution, and is stored separately because it varies between workflows.</t>
+  </si>
+  <si>
+    <t>Transport.output.id</t>
+  </si>
+  <si>
+    <t>Transport.output.extension</t>
+  </si>
+  <si>
+    <t>Transport.output.modifierExtension</t>
+  </si>
+  <si>
+    <t>Transport.output.type</t>
   </si>
   <si>
     <t>Label for output</t>
@@ -1310,13 +1263,13 @@
     <t>The name of the Output parameter.</t>
   </si>
   <si>
-    <t>Outputs are named to enable task automation to bind data and pass it from one task to the next.</t>
+    <t>Outputs are named to enable transport automation to bind data and pass it from one transport to the next.</t>
   </si>
   <si>
     <t>Codes to identify types of input parameters.  These will typically be specific to a particular workflow.  E.g. "Identified issues", "Preliminary results", "Filler order", "Final results", etc.</t>
   </si>
   <si>
-    <t>Task.output.value[x]</t>
+    <t>Transport.output.value[x]</t>
   </si>
   <si>
     <t>Result of output</t>
@@ -1325,7 +1278,62 @@
     <t>The value of the Output parameter as a basic type.</t>
   </si>
   <si>
-    <t>Task outputs can take any form.</t>
+    <t>Transport outputs can take any form.</t>
+  </si>
+  <si>
+    <t>Transport.requestedLocation</t>
+  </si>
+  <si>
+    <t>The desired location</t>
+  </si>
+  <si>
+    <t>The desired or final location for the transport.</t>
+  </si>
+  <si>
+    <t>Transport.currentLocation</t>
+  </si>
+  <si>
+    <t>The entity current location</t>
+  </si>
+  <si>
+    <t>The current location for the entity to be transported.</t>
+  </si>
+  <si>
+    <t>Transport.reason</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableReference(Resource)
+</t>
+  </si>
+  <si>
+    <t>Why transport is needed</t>
+  </si>
+  <si>
+    <t>A resource reference indicating why this transport needs to be performed.</t>
+  </si>
+  <si>
+    <t>Transports might be justified based on an Observation, a Condition, a past or planned procedure, etc. This should only be included if there is no focus or if it differs from the reason indicated on the focus.    Use the CodeableConcept text element in `Transport.reasonCode` if the data is free (uncoded) text.</t>
+  </si>
+  <si>
+    <t>Indicates why the transport is needed.  E.g. Suspended because patient admitted to hospital.</t>
+  </si>
+  <si>
+    <t>Request.reason, Event.reason</t>
+  </si>
+  <si>
+    <t>FiveWs.why[x]</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode=RSON].target</t>
+  </si>
+  <si>
+    <t>Transport.history</t>
+  </si>
+  <si>
+    <t>Parent (or preceding) transport</t>
+  </si>
+  <si>
+    <t>The transport event prior to this one.</t>
   </si>
 </sst>
 </file>
@@ -1474,7 +1482,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -1561,77 +1569,85 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="B13" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>9</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>24</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>25</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="B15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
         <v>34</v>
       </c>
-      <c r="B20" t="s" s="2">
+      <c r="B21" t="s" s="2">
         <v>35</v>
       </c>
     </row>
@@ -1642,11 +1658,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN57"/>
+  <dimension ref="A1:AN58"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="32.42578125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="32.42578125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="37.0390625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="37.0390625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
@@ -1670,7 +1686,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="169.1328125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="45.80078125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="47.90234375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
@@ -1681,9 +1697,9 @@
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="55.72265625" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="109.98828125" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="28.1484375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="109.98828125" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="28.37109375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1914,7 +1930,7 @@
         <v>83</v>
       </c>
       <c r="AM2" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AN2" t="s" s="2">
         <v>76</v>
@@ -1922,10 +1938,10 @@
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -1936,7 +1952,7 @@
         <v>77</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>76</v>
@@ -1945,19 +1961,19 @@
         <v>76</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -2007,13 +2023,13 @@
         <v>76</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>76</v>
@@ -2036,10 +2052,10 @@
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2050,7 +2066,7 @@
         <v>77</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>76</v>
@@ -2059,16 +2075,16 @@
         <v>76</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2119,19 +2135,19 @@
         <v>76</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>76</v>
@@ -2148,10 +2164,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2162,28 +2178,28 @@
         <v>77</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>76</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2233,19 +2249,19 @@
         <v>76</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>76</v>
@@ -2262,10 +2278,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2276,7 +2292,7 @@
         <v>77</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>76</v>
@@ -2288,16 +2304,16 @@
         <v>76</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2323,13 +2339,13 @@
         <v>76</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>76</v>
@@ -2347,19 +2363,19 @@
         <v>76</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>76</v>
@@ -2376,21 +2392,21 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>76</v>
@@ -2402,16 +2418,16 @@
         <v>76</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2461,28 +2477,28 @@
         <v>76</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>76</v>
+        <v>121</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>120</v>
+        <v>76</v>
       </c>
       <c r="AM7" t="s" s="2">
-        <v>76</v>
+        <v>122</v>
       </c>
       <c r="AN7" t="s" s="2">
         <v>76</v>
@@ -2490,14 +2506,14 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -2516,16 +2532,16 @@
         <v>76</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2575,7 +2591,7 @@
         <v>76</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>77</v>
@@ -2584,7 +2600,7 @@
         <v>78</v>
       </c>
       <c r="AI8" t="s" s="2">
-        <v>76</v>
+        <v>130</v>
       </c>
       <c r="AJ8" t="s" s="2">
         <v>76</v>
@@ -2593,10 +2609,10 @@
         <v>76</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>128</v>
+        <v>76</v>
       </c>
       <c r="AM8" t="s" s="2">
-        <v>76</v>
+        <v>131</v>
       </c>
       <c r="AN8" t="s" s="2">
         <v>76</v>
@@ -2604,14 +2620,14 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2630,16 +2646,16 @@
         <v>76</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2689,7 +2705,7 @@
         <v>76</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>77</v>
@@ -2701,16 +2717,16 @@
         <v>76</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>128</v>
+        <v>76</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>76</v>
+        <v>131</v>
       </c>
       <c r="AN9" t="s" s="2">
         <v>76</v>
@@ -2718,14 +2734,14 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -2738,25 +2754,25 @@
         <v>76</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>76</v>
@@ -2805,7 +2821,7 @@
         <v>76</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>77</v>
@@ -2817,16 +2833,16 @@
         <v>76</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>128</v>
+        <v>76</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>76</v>
+        <v>131</v>
       </c>
       <c r="AN10" t="s" s="2">
         <v>76</v>
@@ -2834,10 +2850,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2860,15 +2876,17 @@
         <v>76</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="N11" s="2"/>
+        <v>148</v>
+      </c>
+      <c r="N11" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>76</v>
@@ -2917,7 +2935,7 @@
         <v>76</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>77</v>
@@ -2929,16 +2947,16 @@
         <v>76</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>147</v>
+        <v>76</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="AN11" t="s" s="2">
         <v>76</v>
@@ -2946,10 +2964,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2960,7 +2978,7 @@
         <v>77</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>76</v>
@@ -2969,20 +2987,20 @@
         <v>76</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" t="s" s="2">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>76</v>
@@ -3031,28 +3049,28 @@
         <v>76</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>155</v>
+        <v>76</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>76</v>
+        <v>158</v>
       </c>
       <c r="AN12" t="s" s="2">
         <v>76</v>
@@ -3060,10 +3078,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3074,7 +3092,7 @@
         <v>77</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>76</v>
@@ -3083,20 +3101,20 @@
         <v>76</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>76</v>
@@ -3145,28 +3163,28 @@
         <v>76</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>155</v>
+        <v>76</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>76</v>
+        <v>158</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>76</v>
@@ -3174,10 +3192,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3197,16 +3215,16 @@
         <v>76</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -3257,7 +3275,7 @@
         <v>76</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>77</v>
@@ -3269,16 +3287,16 @@
         <v>76</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>165</v>
+        <v>76</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>76</v>
+        <v>168</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>76</v>
@@ -3286,10 +3304,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3300,7 +3318,7 @@
         <v>77</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>76</v>
@@ -3309,20 +3327,20 @@
         <v>76</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" t="s" s="2">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>76</v>
@@ -3371,28 +3389,28 @@
         <v>76</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>171</v>
+        <v>76</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>76</v>
+        <v>174</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>76</v>
@@ -3400,10 +3418,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3423,22 +3441,22 @@
         <v>76</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>76</v>
@@ -3487,7 +3505,7 @@
         <v>76</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>77</v>
@@ -3499,27 +3517,27 @@
         <v>76</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>179</v>
+        <v>76</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>76</v>
+        <v>182</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>76</v>
+        <v>183</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3527,33 +3545,31 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>76</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="N17" s="2"/>
-      <c r="O17" t="s" s="2">
-        <v>183</v>
-      </c>
+      <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>76</v>
       </c>
@@ -3577,52 +3593,52 @@
         <v>76</v>
       </c>
       <c r="X17" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="Y17" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="Z17" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="AA17" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF17" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="Y17" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="Z17" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="AA17" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB17" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF17" t="s" s="2">
-        <v>180</v>
-      </c>
       <c r="AG17" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>187</v>
+        <v>76</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>76</v>
@@ -3630,10 +3646,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3644,7 +3660,7 @@
         <v>77</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>76</v>
@@ -3653,19 +3669,19 @@
         <v>76</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3691,13 +3707,13 @@
         <v>76</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>76</v>
+        <v>198</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>76</v>
@@ -3715,28 +3731,28 @@
         <v>76</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>196</v>
+        <v>76</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>76</v>
+        <v>199</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>76</v>
@@ -3744,10 +3760,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3755,10 +3771,10 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>76</v>
@@ -3767,21 +3783,21 @@
         <v>76</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>190</v>
+        <v>106</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="N19" s="2"/>
-      <c r="O19" t="s" s="2">
-        <v>200</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>76</v>
       </c>
@@ -3805,13 +3821,13 @@
         <v>76</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>194</v>
+        <v>110</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>76</v>
+        <v>205</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>76</v>
@@ -3829,28 +3845,28 @@
         <v>76</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>76</v>
+        <v>206</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>76</v>
+        <v>208</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>76</v>
@@ -3858,10 +3874,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3869,10 +3885,10 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>76</v>
@@ -3881,25 +3897,27 @@
         <v>76</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="O20" s="2"/>
+        <v>211</v>
+      </c>
+      <c r="N20" s="2"/>
+      <c r="O20" t="s" s="2">
+        <v>212</v>
+      </c>
       <c r="P20" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="Q20" s="2"/>
+      <c r="Q20" t="s" s="2">
+        <v>213</v>
+      </c>
       <c r="R20" t="s" s="2">
         <v>76</v>
       </c>
@@ -3919,13 +3937,13 @@
         <v>76</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>184</v>
+        <v>110</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>76</v>
@@ -3943,28 +3961,28 @@
         <v>76</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>76</v>
@@ -3972,10 +3990,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3986,7 +4004,7 @@
         <v>77</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>76</v>
@@ -3995,27 +4013,25 @@
         <v>76</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>105</v>
+        <v>192</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="N21" s="2"/>
-      <c r="O21" t="s" s="2">
-        <v>215</v>
-      </c>
+        <v>221</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="Q21" t="s" s="2">
-        <v>216</v>
-      </c>
+      <c r="Q21" s="2"/>
       <c r="R21" t="s" s="2">
         <v>76</v>
       </c>
@@ -4035,13 +4051,13 @@
         <v>76</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>76</v>
@@ -4059,28 +4075,28 @@
         <v>76</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>76</v>
@@ -4088,10 +4104,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4102,7 +4118,7 @@
         <v>77</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>76</v>
@@ -4111,20 +4127,18 @@
         <v>76</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>190</v>
+        <v>229</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>225</v>
-      </c>
+        <v>231</v>
+      </c>
+      <c r="N22" s="2"/>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>76</v>
@@ -4149,13 +4163,13 @@
         <v>76</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>194</v>
+        <v>76</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>226</v>
+        <v>76</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>227</v>
+        <v>76</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>76</v>
@@ -4173,28 +4187,28 @@
         <v>76</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>228</v>
+        <v>76</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>229</v>
+        <v>76</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>76</v>
@@ -4202,10 +4216,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4216,7 +4230,7 @@
         <v>77</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>76</v>
@@ -4225,19 +4239,23 @@
         <v>76</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>232</v>
+        <v>164</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="N23" s="2"/>
-      <c r="O23" s="2"/>
+        <v>235</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="O23" t="s" s="2">
+        <v>237</v>
+      </c>
       <c r="P23" t="s" s="2">
         <v>76</v>
       </c>
@@ -4285,28 +4303,28 @@
         <v>76</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>76</v>
+        <v>238</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>76</v>
@@ -4314,21 +4332,21 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>76</v>
+        <v>240</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>76</v>
@@ -4337,22 +4355,20 @@
         <v>76</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>239</v>
-      </c>
+        <v>242</v>
+      </c>
+      <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>76</v>
@@ -4401,28 +4417,28 @@
         <v>76</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>76</v>
+        <v>244</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>230</v>
+        <v>246</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>76</v>
@@ -4430,21 +4446,21 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>243</v>
+        <v>76</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>76</v>
@@ -4453,20 +4469,20 @@
         <v>76</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>161</v>
+        <v>248</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>76</v>
@@ -4515,28 +4531,28 @@
         <v>76</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>76</v>
@@ -4544,10 +4560,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4558,7 +4574,7 @@
         <v>77</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>76</v>
@@ -4567,21 +4583,19 @@
         <v>76</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="N26" s="2"/>
-      <c r="O26" t="s" s="2">
-        <v>254</v>
-      </c>
+      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>76</v>
       </c>
@@ -4629,28 +4643,28 @@
         <v>76</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>76</v>
@@ -4658,21 +4672,21 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>76</v>
+        <v>263</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>76</v>
@@ -4681,19 +4695,21 @@
         <v>76</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="N27" s="2"/>
-      <c r="O27" s="2"/>
+      <c r="O27" t="s" s="2">
+        <v>266</v>
+      </c>
       <c r="P27" t="s" s="2">
         <v>76</v>
       </c>
@@ -4741,28 +4757,28 @@
         <v>76</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>76</v>
@@ -4770,21 +4786,21 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>76</v>
@@ -4793,20 +4809,20 @@
         <v>76</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>267</v>
+        <v>256</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" t="s" s="2">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>76</v>
@@ -4855,28 +4871,28 @@
         <v>76</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>271</v>
+        <v>76</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>272</v>
+        <v>76</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>273</v>
+        <v>76</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>76</v>
@@ -4884,21 +4900,21 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>276</v>
+        <v>76</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>76</v>
@@ -4907,20 +4923,20 @@
         <v>76</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>76</v>
@@ -4969,28 +4985,28 @@
         <v>76</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>271</v>
+        <v>76</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>76</v>
+        <v>281</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>76</v>
+        <v>283</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>76</v>
@@ -4998,10 +5014,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5012,7 +5028,7 @@
         <v>77</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>76</v>
@@ -5021,20 +5037,20 @@
         <v>76</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>282</v>
+        <v>192</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>76</v>
@@ -5059,13 +5075,13 @@
         <v>76</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>76</v>
+        <v>288</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>76</v>
+        <v>289</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>76</v>
+        <v>290</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>76</v>
@@ -5083,28 +5099,28 @@
         <v>76</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>76</v>
@@ -5112,21 +5128,21 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>76</v>
+        <v>295</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>76</v>
@@ -5135,20 +5151,22 @@
         <v>76</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>190</v>
+        <v>296</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="N31" s="2"/>
+        <v>298</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>299</v>
+      </c>
       <c r="O31" t="s" s="2">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>76</v>
@@ -5173,52 +5191,52 @@
         <v>76</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>109</v>
+        <v>76</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>293</v>
+        <v>76</v>
       </c>
       <c r="Z31" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA31" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB31" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD31" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE31" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF31" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="AA31" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB31" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC31" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD31" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE31" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF31" t="s" s="2">
-        <v>289</v>
-      </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>76</v>
@@ -5226,21 +5244,21 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>299</v>
+        <v>76</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>76</v>
@@ -5249,22 +5267,20 @@
         <v>76</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>303</v>
-      </c>
+        <v>306</v>
+      </c>
+      <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>76</v>
@@ -5313,28 +5329,28 @@
         <v>76</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>305</v>
+        <v>76</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>297</v>
+        <v>309</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>76</v>
@@ -5342,10 +5358,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5356,7 +5372,7 @@
         <v>77</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>76</v>
@@ -5365,21 +5381,19 @@
         <v>76</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="N33" s="2"/>
-      <c r="O33" t="s" s="2">
-        <v>311</v>
-      </c>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>76</v>
       </c>
@@ -5427,39 +5441,39 @@
         <v>76</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>313</v>
+        <v>76</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>76</v>
+        <v>316</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5470,10 +5484,10 @@
         <v>77</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>76</v>
@@ -5482,17 +5496,15 @@
         <v>76</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>190</v>
+        <v>318</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>318</v>
-      </c>
+        <v>320</v>
+      </c>
+      <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>76</v>
@@ -5517,10 +5529,10 @@
         <v>76</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>194</v>
+        <v>76</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>319</v>
+        <v>76</v>
       </c>
       <c r="Z34" t="s" s="2">
         <v>76</v>
@@ -5541,50 +5553,50 @@
         <v>76</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>321</v>
+        <v>76</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>322</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>323</v>
+        <v>76</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>76</v>
+        <v>324</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>76</v>
@@ -5596,16 +5608,16 @@
         <v>76</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>161</v>
+        <v>325</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>316</v>
+        <v>326</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5655,28 +5667,28 @@
         <v>76</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>328</v>
+        <v>76</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>76</v>
@@ -5684,10 +5696,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5698,7 +5710,7 @@
         <v>77</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>76</v>
@@ -5710,16 +5722,18 @@
         <v>76</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="N36" s="2"/>
-      <c r="O36" s="2"/>
+      <c r="O36" t="s" s="2">
+        <v>335</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>76</v>
       </c>
@@ -5767,39 +5781,39 @@
         <v>76</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>333</v>
+        <v>76</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>334</v>
+        <v>76</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>76</v>
+        <v>336</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>335</v>
+        <v>76</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5810,10 +5824,10 @@
         <v>77</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>76</v>
@@ -5822,7 +5836,7 @@
         <v>76</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>337</v>
+        <v>229</v>
       </c>
       <c r="L37" t="s" s="2">
         <v>338</v>
@@ -5879,28 +5893,28 @@
         <v>76</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>76</v>
+        <v>341</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>340</v>
+        <v>76</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>341</v>
+        <v>76</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>76</v>
+        <v>342</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>76</v>
@@ -5908,14 +5922,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>343</v>
+        <v>133</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -5934,16 +5948,16 @@
         <v>76</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L38" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="L38" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>346</v>
-      </c>
       <c r="N38" t="s" s="2">
-        <v>347</v>
+        <v>137</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5993,7 +6007,7 @@
         <v>76</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>77</v>
@@ -6005,16 +6019,16 @@
         <v>76</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>97</v>
+        <v>139</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>348</v>
+        <v>76</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>349</v>
+        <v>76</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>76</v>
+        <v>342</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>76</v>
@@ -6022,43 +6036,45 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>76</v>
+        <v>347</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>76</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>351</v>
+        <v>134</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>349</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="O39" t="s" s="2">
-        <v>354</v>
+        <v>143</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>76</v>
@@ -6113,22 +6129,22 @@
         <v>77</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>97</v>
+        <v>139</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>355</v>
+        <v>76</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>76</v>
+        <v>131</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>76</v>
@@ -6136,10 +6152,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6150,7 +6166,7 @@
         <v>77</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>76</v>
@@ -6162,16 +6178,18 @@
         <v>76</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>232</v>
+        <v>352</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="N40" s="2"/>
-      <c r="O40" s="2"/>
+      <c r="O40" t="s" s="2">
+        <v>355</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>76</v>
       </c>
@@ -6219,28 +6237,28 @@
         <v>76</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>360</v>
+        <v>76</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>76</v>
+        <v>356</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>76</v>
@@ -6248,21 +6266,21 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>130</v>
+        <v>76</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>76</v>
@@ -6274,18 +6292,20 @@
         <v>76</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>131</v>
+        <v>358</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>132</v>
+        <v>359</v>
       </c>
       <c r="M41" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="O41" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="N41" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>76</v>
       </c>
@@ -6333,28 +6353,28 @@
         <v>76</v>
       </c>
       <c r="AF41" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="AG41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH41" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI41" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ41" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK41" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM41" t="s" s="2">
         <v>363</v>
-      </c>
-      <c r="AG41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI41" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ41" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="AK41" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AL41" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="AM41" t="s" s="2">
-        <v>76</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>76</v>
@@ -6369,7 +6389,7 @@
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>365</v>
+        <v>76</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6382,13 +6402,13 @@
         <v>76</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>131</v>
+        <v>365</v>
       </c>
       <c r="L42" t="s" s="2">
         <v>366</v>
@@ -6396,12 +6416,8 @@
       <c r="M42" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="N42" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>140</v>
-      </c>
+      <c r="N42" s="2"/>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>76</v>
       </c>
@@ -6449,7 +6465,7 @@
         <v>76</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>77</v>
@@ -6461,16 +6477,16 @@
         <v>76</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>136</v>
+        <v>98</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>128</v>
+        <v>76</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>76</v>
+        <v>368</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>76</v>
@@ -6485,14 +6501,14 @@
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>76</v>
+        <v>370</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>76</v>
@@ -6504,7 +6520,7 @@
         <v>76</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>370</v>
+        <v>332</v>
       </c>
       <c r="L43" t="s" s="2">
         <v>371</v>
@@ -6569,22 +6585,22 @@
         <v>77</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL43" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM43" t="s" s="2">
         <v>374</v>
-      </c>
-      <c r="AM43" t="s" s="2">
-        <v>76</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>76</v>
@@ -6606,7 +6622,7 @@
         <v>77</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>76</v>
@@ -6618,20 +6634,16 @@
         <v>76</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>259</v>
+        <v>229</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>376</v>
+        <v>338</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>379</v>
-      </c>
+        <v>339</v>
+      </c>
+      <c r="N44" s="2"/>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>76</v>
       </c>
@@ -6679,28 +6691,28 @@
         <v>76</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>375</v>
+        <v>340</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>76</v>
+        <v>341</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>380</v>
+        <v>76</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>76</v>
+        <v>342</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>76</v>
@@ -6708,14 +6720,14 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>76</v>
+        <v>133</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -6734,15 +6746,17 @@
         <v>76</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>382</v>
+        <v>134</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>383</v>
+        <v>135</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="N45" s="2"/>
+        <v>344</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>76</v>
@@ -6791,7 +6805,7 @@
         <v>76</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>381</v>
+        <v>345</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>77</v>
@@ -6803,16 +6817,16 @@
         <v>76</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>97</v>
+        <v>139</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>385</v>
+        <v>76</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>76</v>
+        <v>342</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>76</v>
@@ -6820,14 +6834,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>387</v>
+        <v>347</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -6840,23 +6854,25 @@
         <v>76</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>351</v>
+        <v>134</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>388</v>
+        <v>348</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="N46" s="2"/>
+        <v>349</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="O46" t="s" s="2">
-        <v>390</v>
+        <v>143</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>76</v>
@@ -6905,7 +6921,7 @@
         <v>76</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>386</v>
+        <v>350</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>77</v>
@@ -6917,16 +6933,16 @@
         <v>76</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>97</v>
+        <v>139</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>391</v>
+        <v>76</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>76</v>
+        <v>131</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>76</v>
@@ -6934,21 +6950,21 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>392</v>
+        <v>378</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>392</v>
+        <v>378</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>76</v>
+        <v>379</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>76</v>
@@ -6960,16 +6976,20 @@
         <v>76</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>357</v>
+        <v>380</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="N47" s="2"/>
-      <c r="O47" s="2"/>
+        <v>381</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>383</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>76</v>
       </c>
@@ -6993,10 +7013,10 @@
         <v>76</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>76</v>
+        <v>196</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>76</v>
+        <v>384</v>
       </c>
       <c r="Z47" t="s" s="2">
         <v>76</v>
@@ -7017,28 +7037,28 @@
         <v>76</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>359</v>
+        <v>378</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>360</v>
+        <v>76</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>76</v>
+        <v>374</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>76</v>
@@ -7046,21 +7066,21 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>393</v>
+        <v>385</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>393</v>
+        <v>385</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>130</v>
+        <v>76</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>76</v>
@@ -7072,17 +7092,15 @@
         <v>76</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>131</v>
+        <v>386</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>132</v>
+        <v>387</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>134</v>
-      </c>
+        <v>388</v>
+      </c>
+      <c r="N48" s="2"/>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>76</v>
@@ -7131,28 +7149,28 @@
         <v>76</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>363</v>
+        <v>385</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>136</v>
+        <v>98</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>360</v>
+        <v>76</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>76</v>
+        <v>374</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>76</v>
@@ -7160,14 +7178,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>365</v>
+        <v>76</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7180,25 +7198,23 @@
         <v>76</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>131</v>
+        <v>332</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>366</v>
+        <v>390</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>134</v>
-      </c>
+        <v>391</v>
+      </c>
+      <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>140</v>
+        <v>392</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>76</v>
@@ -7247,7 +7263,7 @@
         <v>76</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>368</v>
+        <v>389</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>77</v>
@@ -7259,16 +7275,16 @@
         <v>76</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>136</v>
+        <v>98</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>128</v>
+        <v>76</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>76</v>
+        <v>374</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>76</v>
@@ -7276,21 +7292,21 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>396</v>
+        <v>76</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>76</v>
@@ -7302,20 +7318,16 @@
         <v>76</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>190</v>
+        <v>229</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>397</v>
+        <v>338</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>400</v>
-      </c>
+        <v>339</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>76</v>
       </c>
@@ -7339,10 +7351,10 @@
         <v>76</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>194</v>
+        <v>76</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>401</v>
+        <v>76</v>
       </c>
       <c r="Z50" t="s" s="2">
         <v>76</v>
@@ -7363,28 +7375,28 @@
         <v>76</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>395</v>
+        <v>340</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>76</v>
+        <v>341</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>391</v>
+        <v>76</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>76</v>
+        <v>342</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>76</v>
@@ -7392,21 +7404,21 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>76</v>
+        <v>133</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>76</v>
@@ -7418,15 +7430,17 @@
         <v>76</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>403</v>
+        <v>134</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>404</v>
+        <v>135</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="N51" s="2"/>
+        <v>344</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>76</v>
@@ -7475,28 +7489,28 @@
         <v>76</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>402</v>
+        <v>345</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>97</v>
+        <v>139</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>391</v>
+        <v>76</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>76</v>
+        <v>342</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>76</v>
@@ -7504,14 +7518,14 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>406</v>
+        <v>395</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>406</v>
+        <v>395</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>76</v>
+        <v>347</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -7524,23 +7538,25 @@
         <v>76</v>
       </c>
       <c r="I52" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>351</v>
+        <v>134</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>407</v>
+        <v>348</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="N52" s="2"/>
+        <v>349</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="O52" t="s" s="2">
-        <v>409</v>
+        <v>143</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>76</v>
@@ -7589,7 +7605,7 @@
         <v>76</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>406</v>
+        <v>350</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>77</v>
@@ -7601,16 +7617,16 @@
         <v>76</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>97</v>
+        <v>139</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>391</v>
+        <v>76</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>76</v>
+        <v>131</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>76</v>
@@ -7618,21 +7634,21 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>410</v>
+        <v>396</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>410</v>
+        <v>396</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>76</v>
+        <v>379</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>76</v>
@@ -7644,16 +7660,18 @@
         <v>76</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>357</v>
+        <v>397</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>358</v>
+        <v>398</v>
       </c>
       <c r="N53" s="2"/>
-      <c r="O53" s="2"/>
+      <c r="O53" t="s" s="2">
+        <v>399</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>76</v>
       </c>
@@ -7677,10 +7695,10 @@
         <v>76</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>76</v>
+        <v>196</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>76</v>
+        <v>400</v>
       </c>
       <c r="Z53" t="s" s="2">
         <v>76</v>
@@ -7701,28 +7719,28 @@
         <v>76</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>359</v>
+        <v>396</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>360</v>
+        <v>76</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>76</v>
+        <v>374</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>76</v>
@@ -7730,21 +7748,21 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>411</v>
+        <v>401</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>411</v>
+        <v>401</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>130</v>
+        <v>76</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>76</v>
@@ -7756,18 +7774,18 @@
         <v>76</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>131</v>
+        <v>386</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>132</v>
+        <v>402</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="O54" s="2"/>
+        <v>403</v>
+      </c>
+      <c r="N54" s="2"/>
+      <c r="O54" t="s" s="2">
+        <v>404</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>76</v>
       </c>
@@ -7815,28 +7833,28 @@
         <v>76</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>363</v>
+        <v>401</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>136</v>
+        <v>98</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>360</v>
+        <v>76</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>76</v>
+        <v>374</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>76</v>
@@ -7844,46 +7862,42 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>412</v>
+        <v>405</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>412</v>
+        <v>405</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>365</v>
+        <v>76</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>76</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>131</v>
+        <v>304</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>366</v>
+        <v>406</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>407</v>
+      </c>
+      <c r="N55" s="2"/>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>76</v>
       </c>
@@ -7931,28 +7945,28 @@
         <v>76</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>368</v>
+        <v>405</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>136</v>
+        <v>98</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>128</v>
+        <v>308</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>76</v>
+        <v>309</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>76</v>
@@ -7960,21 +7974,21 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>396</v>
+        <v>76</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>76</v>
@@ -7983,21 +7997,19 @@
         <v>76</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>190</v>
+        <v>304</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="N56" s="2"/>
-      <c r="O56" t="s" s="2">
-        <v>416</v>
-      </c>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>76</v>
       </c>
@@ -8021,10 +8033,10 @@
         <v>76</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>194</v>
+        <v>76</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>417</v>
+        <v>76</v>
       </c>
       <c r="Z56" t="s" s="2">
         <v>76</v>
@@ -8045,28 +8057,28 @@
         <v>76</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>391</v>
+        <v>308</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>76</v>
+        <v>309</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>76</v>
@@ -8074,10 +8086,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8085,10 +8097,10 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>76</v>
@@ -8100,18 +8112,18 @@
         <v>76</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>403</v>
+        <v>412</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="N57" s="2"/>
-      <c r="O57" t="s" s="2">
-        <v>421</v>
-      </c>
+        <v>414</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>76</v>
       </c>
@@ -8135,10 +8147,10 @@
         <v>76</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>76</v>
+        <v>196</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>76</v>
+        <v>416</v>
       </c>
       <c r="Z57" t="s" s="2">
         <v>76</v>
@@ -8159,35 +8171,147 @@
         <v>76</v>
       </c>
       <c r="AF57" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="AL57" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="AG57" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH57" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI57" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ57" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AK57" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AL57" t="s" s="2">
-        <v>391</v>
-      </c>
       <c r="AM57" t="s" s="2">
-        <v>76</v>
+        <v>419</v>
       </c>
       <c r="AN57" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="58" hidden="true">
+      <c r="A58" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J58" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K58" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="N58" s="2"/>
+      <c r="O58" s="2"/>
+      <c r="P58" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q58" s="2"/>
+      <c r="R58" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S58" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="AN58" t="s" s="2">
         <v>76</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN57">
+  <autoFilter ref="A1:AN58">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -8197,7 +8321,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI56">
+  <conditionalFormatting sqref="A2:AI57">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/branches/master/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/branches/master/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T19:02:34+00:00</t>
+    <t>2023-05-11T19:57:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/branches/master/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T19:57:24+00:00</t>
+    <t>2023-05-11T20:42:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/branches/master/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T20:42:55+00:00</t>
+    <t>2023-05-12T08:27:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/branches/master/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T08:27:31+00:00</t>
+    <t>2023-05-12T10:53:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/branches/master/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T10:53:52+00:00</t>
+    <t>2023-05-12T13:58:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-result-dispatched-to-facility.xlsx
+++ b/branches/master/StructureDefinition-result-dispatched-to-facility.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T13:58:20+00:00</t>
+    <t>2023-05-23T09:20:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
